--- a/.source/category_table.xlsx
+++ b/.source/category_table.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E177"/>
+  <dimension ref="A1:E214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,518 +436,726 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>위험도</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>카테고리</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>위험지표</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>키워드</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>카테고리</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>위험도</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>업종코드</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>전처리</t>
+          <t>계정과목</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>023 shop</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>023복권</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+          <t>X_기타</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>X01</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>(입금방향자동배정)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>전처리</t>
+          <t>계정과목</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HN</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>농협</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+          <t>X_기타</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>X02</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>나래/더에덴/라프/로그인/로스</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>전처리</t>
+          <t>계정과목</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>KB</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>국민</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+          <t>X_기타</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>X02</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>마이/메머드/메트로/몽실/미성</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>전처리</t>
+          <t>계정과목</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>나눔과어울림</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>빗썸</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+          <t>X_기타</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>X02</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>보타나/아이지/에델/에스지씨/에이스</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>전처리</t>
+          <t>계정과목</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>남동기업센터</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>남동기업명품센터</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+          <t>X_기타</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>X02</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>엠에스/올댓/와이에스/월드/유니윌</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>전처리</t>
+          <t>계정과목</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>도이</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>김도이</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+          <t>X_기타</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>X02</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>이투유/제이디/클락에이/플래티넘/황실</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>전처리</t>
+          <t>계정과목</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>성우서비스</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>성우머니대부</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+          <t>X_기타</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>X03</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>(은행미매칭입금자동배정)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>전처리</t>
+          <t>계정과목</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>씨워크</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>씨워크안마</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+          <t>X_기타</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>X04</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>(은행미매칭출금자동배정)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>전처리</t>
+          <t>계정과목</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>어머니/시엄마/어머니</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>한경숙</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
+          <t>X_기타</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>X05</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>(카드미매칭입금자동배정)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>전처리</t>
+          <t>계정과목</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>에이치앤케이산업개발</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>가상자산</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
+          <t>X_기타</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>X06</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>(카드미매칭출금자동배정)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>전처리</t>
+          <t>계정과목</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>운영</t>
+          <t>I_자금이동</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>문영안마</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
+          <t>M_계좌이동</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>M01</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>모바일/오픈뱅킹/인터넷/전자금융/지로</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>전처리</t>
+          <t>계정과목</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>은샘</t>
+          <t>I_자금이동</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>김은샘</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
+          <t>M_계좌이동</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>M01</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>대외기관/스마트출금/외국환/전자민원/체크할인/펌뱅킹/환급인천</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>전처리</t>
+          <t>계정과목</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>의료법인 나사렛의료재단</t>
+          <t>I_자금이동</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>나사렛마사지</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
+          <t>M_계좌이동</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>M02</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>국민카드/신한카드/이음카드/체크카드/하나카드</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>전처리</t>
+          <t>계정과목</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>전각</t>
+          <t>I_자금이동</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>반각</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
+          <t>M_계좌이동</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>M02</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>현대카드</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>전처리</t>
+          <t>계정과목</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>주금공</t>
+          <t>II_필수생활비</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>주택금융공사</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
+          <t>L_건강/교육</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>L06</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>건강보험/견생냥품/나사렛/내과/동물의료</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>전처리</t>
+          <t>계정과목</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>주식회사/ 주식회사 / 주식회사</t>
+          <t>II_필수생활비</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>(주)</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
+          <t>L_건강/교육</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>L06</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>레푸스/메디컬/병원/복지용구/사랑의마을</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>전처리</t>
+          <t>계정과목</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>친애저축</t>
+          <t>II_필수생활비</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>친애저축P2P</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
+          <t>L_건강/교육</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>L06</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>신경외과/안과/약국/엄마손/워너독</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>전처리</t>
+          <t>계정과목</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>하나오픈에이치</t>
+          <t>II_필수생활비</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>하나유흥주점</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
+          <t>L_건강/교육</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>L06</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>의료법인/의원/이비인후과/이선아/정형외과</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>전처리</t>
+          <t>계정과목</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>한국주택은행</t>
+          <t>II_필수생활비</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>국민은행</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
+          <t>L_건강/교육</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>L06</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>치과</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>전처리</t>
+          <t>계정과목</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>II_필수생활비</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>현대백화점</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
+          <t>L_건강/교육</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>L07</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>건설기술/교보문고</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>후처리</t>
+          <t>계정과목</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>((</t>
+          <t>II_필수생활비</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>(</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
+          <t>L_교통/보험</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>L05</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>29가8142/60도2787/교통/국민오일/기아오토큐</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>후처리</t>
+          <t>계정과목</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>))</t>
+          <t>II_필수생활비</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>)</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
+          <t>L_교통/보험</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>L05</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>도로/도로공사/로드801/만월산/모빌리티</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>후처리</t>
+          <t>계정과목</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>II_필수생활비</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>space</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
+          <t>L_교통/보험</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>L05</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>문학개발/문학터널/버스/북서울에너지/선학현대</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>후처리</t>
+          <t>계정과목</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>김김은샘</t>
+          <t>II_필수생활비</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>김은샘</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
+          <t>L_교통/보험</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>L05</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>시설공단/시설관리/시설안전/에너지/에이티씨</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>신청인</t>
+          <t>계정과목</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>k30035600@gmail.com/010-3003-5600</t>
+          <t>II_필수생활비</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>김찬식</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
+          <t>L_교통/보험</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>L05</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>인천30/인천32/자동차/주유비/주유소</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>심야구분</t>
+          <t>계정과목</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>22:00:00/06:00:00</t>
+          <t>II_필수생활비</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>심야구분</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
+          <t>L_교통/보험</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>L05</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>지하철/차량유지/철도/칼텍스/코레일</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -957,16 +1165,24 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>파리바게뜨/베이커리</t>
+          <t>II_필수생활비</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>외식/회식/간식</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
+          <t>L_교통/보험</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>L05</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>태리/택시/티머니/파킹/현대오일</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -976,16 +1192,24 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>씨유/CU/서진태</t>
+          <t>II_필수생활비</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>기타잡비</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
+          <t>L_교통/보험</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>L05</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>후불교통</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -995,16 +1219,24 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>(주)이마트/롯데마트/식자재/이마트</t>
+          <t>II_필수생활비</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>주식비/부식비</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
+          <t>L_교통/보험</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>L08</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>메리츠/보험료/자동차보험/차량보험/캐롯</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1014,16 +1246,24 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>가전/의류/가구/제습기/냉장고</t>
+          <t>II_필수생활비</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>가전/가구/의류/생필품</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
+          <t>L_교통/보험</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>L08</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>현대해상/홍세일/홍천일/이영숙</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1033,16 +1273,24 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>비와이씨/삼성전자/현대아울렛/나무다움/어패럴</t>
+          <t>II_필수생활비</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>가전/가구/의류/생필품</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
+          <t>L_식비</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>SSG/건어물/과일/농산물/롯데마트</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1052,16 +1300,24 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>스퀘어/자라/공영쇼핑/에이비씨/이랜드</t>
+          <t>II_필수생활비</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>가전/가구/의류/생필품</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
+          <t>L_식비</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>반찬/부식/생선/성필립보/세계로</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1071,16 +1327,24 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>몰테일/이케아/버킷/신세계/올리브영/LIVING</t>
+          <t>II_필수생활비</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>가전/가구/의류/생필품</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
+          <t>L_식비</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>슈퍼/식자재/야채/우아한/웅이</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1090,16 +1354,24 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>버스/택시/차량유지/자동차/지하철/칼텍스/자동차보험</t>
+          <t>II_필수생활비</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>차량유지/교통비</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
+          <t>L_식비</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>이마트/정육점/주식/코스트코/푸줏간</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1109,16 +1381,24 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>북서울에너지/피킹/도로공사/티머니/에이티씨/차량보험</t>
+          <t>II_필수생활비</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>차량유지/교통비</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
+          <t>L_식비</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>홈마트/홈플러스</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1128,16 +1408,24 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>인천30/인천32/시설공단/문학터널/문학개발/주유소</t>
+          <t>II_필수생활비</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>차량유지/교통비</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
+          <t>L_식비</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>10월/공간븟/공차/국밥/국수</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1147,16 +1435,24 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>만월산/선학현대/후불교통/로드801/에너지/시설안전</t>
+          <t>II_필수생활비</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>차량유지/교통비</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
+          <t>L_식비</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>굴사냥/김밥/김치/낙지/능허대</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1166,16 +1462,24 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>파킹/현대오일/태리/코레일/철도/교통</t>
+          <t>II_필수생활비</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>차량유지/교통비</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
+          <t>L_식비</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>다온나/다정이네/닭강정/닭곰탕/닭소리</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1185,16 +1489,24 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>시설관리/기아오토큐/시설공단/국민오일</t>
+          <t>II_필수생활비</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>차량유지/교통비</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
+          <t>L_식비</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>닭집/대신기업/더달달/던킨/도미노</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1204,16 +1516,24 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>금은방/귀금속/거래소/백화점/명품</t>
+          <t>II_필수생활비</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>귀금속/유흥</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
+          <t>L_식비</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>돈풀/동춘옥/동태촌/두루담채/두부</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1223,16 +1543,24 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>클락에이/CU/GS/쿠팡/네이버/후이즈/타이거</t>
+          <t>II_필수생활비</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>기타잡비</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
+          <t>L_식비</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>두찜/떡방아/뜰아래/롯데리아/마장동</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1242,16 +1570,24 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>토스/쇼핑몰/쇼핑/보타나/공공기관/결재대행/결제대행</t>
+          <t>II_필수생활비</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>기타잡비</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
+          <t>L_식비</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>막국수/만강홍/맛있는죽/매반/맥도날드</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1261,16 +1597,24 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>NICE/SMS/면세점/제이디/라프/씨유/플라워</t>
+          <t>II_필수생활비</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>기타잡비</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
+          <t>L_식비</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>메가/메고/메밀국수/멕시카나/모미락</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1280,16 +1624,24 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>엠에스/세탁소/세븐일레븐/법원/미앤미/헤어/지에스</t>
+          <t>II_필수생활비</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>기타잡비</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
+          <t>L_식비</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>모밀/모밀방/물고기/미두야/미스터</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1299,16 +1651,24 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>예스이십사/코리아세븐/건설기술/티몬/에이스</t>
+          <t>II_필수생활비</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>기타잡비</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
+          <t>L_식비</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>민영/바로/바이/반점/베이커리</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1318,16 +1678,24 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>다온나/아이지/미니스톱/월드/이투유/나이스</t>
+          <t>II_필수생활비</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>기타잡비</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
+          <t>L_식비</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>보리밥/본죽/부대/부대찌게/부원집</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1337,16 +1705,24 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>더에덴/옥션/나래/로그인/메트로/홈엔/ARS/카카오</t>
+          <t>II_필수생활비</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>기타잡비</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
+          <t>L_식비</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>불닭발/블랙벤자민/빽다방/사계절/산자락에</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1356,16 +1732,24 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>와이에스/다날/홈마트/슈퍼/로웰/유니윌/코페이</t>
+          <t>II_필수생활비</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>기타잡비</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
+          <t>L_식비</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>삼계탕/상사/상회/새록/생오리</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1375,16 +1759,24 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>스테이지/이마트24/부경/에스씨/목욕탕/구글</t>
+          <t>II_필수생활비</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>기타잡비</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
+          <t>L_식비</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>선학사골/소바/손만두/솔도갈매기/송도갈매기</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1394,16 +1786,24 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>다이소/빈티지/마이리얼/홈쇼핑/올댓/그릇/로스</t>
+          <t>II_필수생활비</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>기타잡비</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
+          <t>L_식비</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>수산/순대/스마일/스타벅스/식당</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1413,16 +1813,24 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>컬리페이/키오스크/에스지씨/에델/크린토피아/미성</t>
+          <t>II_필수생활비</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>기타잡비</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
+          <t>L_식비</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>씨푸드/아구/아방궁/안스/애월</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1432,16 +1840,24 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>블랙벤자민/LIVING/슬립/세탁/만물/그릇/유진/두찜</t>
+          <t>II_필수생활비</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>기타잡비</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
+          <t>L_식비</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>야래향/어부장/어시장/얼음/엔제리너스</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1451,16 +1867,24 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>티무/황실/KICC/KCP/마이/플래티넘/몽실/가위</t>
+          <t>II_필수생활비</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>기타잡비</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
+          <t>L_식비</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>연어/연쭈/연탄/오구본가/오케이</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1470,16 +1894,24 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>우정사업/유창훈/오영은/최성숙</t>
+          <t>II_필수생활비</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>기타잡비</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
+          <t>L_식비</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>옹진/왕냉면/외식/웨이업/이디야</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1489,16 +1921,24 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>오락/취미/레저/휴양/교보문고/스포츠</t>
+          <t>II_필수생활비</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>레저/휴양/취미/오락</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
+          <t>L_식비</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>이학/자판기/장수마을/저푸른/제주도</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1508,16 +1948,24 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>중국동방/CGV</t>
+          <t>II_필수생활비</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>레저/휴양/취미/오락</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
+          <t>L_식비</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>조개/족발/직화/천상/청량산</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1527,16 +1975,24 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>외식/회식/호치킨/콩닭/모밀방/상회/필/삼계탕</t>
+          <t>II_필수생활비</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>외식/회식/간식</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
+          <t>L_식비</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>최부자네/추어탕/카페/카페온/칼국수</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1546,16 +2002,24 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>제주도/애월/바이/해장국/족발/연쭈/모미락/도미노</t>
+          <t>II_필수생활비</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>외식/회식/간식</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
+          <t>L_식비</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>컴포즈/콩닭/콩세알/타이거/통닭</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1565,16 +2029,24 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>맛있는죽/맥도날드/새록/칼국수/순대/식당/롯데리아</t>
+          <t>II_필수생활비</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>외식/회식/간식</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
+          <t>L_식비</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>투썸/파리바게뜨/패류/페리카나/포베이</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1584,16 +2056,24 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>오구본가/연탄/파리바게뜨/타이거/김치/수산/국수</t>
+          <t>II_필수생활비</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>외식/회식/간식</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
+          <t>L_식비</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>푸드/필/할매/해장국/호치킨</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1603,16 +2083,24 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>선학사골/천상/메가/스타벅스/엔제리너스/리너스</t>
+          <t>II_필수생활비</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>외식/회식/간식</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
+          <t>L_식비</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>회식/휴게소</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1622,16 +2110,24 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>추어탕/야래향</t>
+          <t>II_필수생활비</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>외식/회식/간식</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr"/>
+          <t>L_주거/통신</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>L03</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>관리비/성우서비스/씨워크/오석경/전세보증금</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1641,16 +2137,24 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>더달달/컴포즈/닭집/할매/동태촌/왕냉면/통닭/아구</t>
+          <t>II_필수생활비</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>외식/회식/간식</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr"/>
+          <t>L_주거/통신</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>L03</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>조형호/최현희/푸른날개/풍림3차/풍림연수</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1660,16 +2164,24 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>추어탕/부대/부대찌게/보리밥/본죽/카페/안스/식당</t>
+          <t>II_필수생활비</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>외식/회식/간식</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr"/>
+          <t>L_주거/통신</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>L03</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>하희숙깨비익스프레</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1679,16 +2191,24 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>아방궁/돈풀/카페온/부원집/능허대/옹진/상사/국밥</t>
+          <t>II_필수생활비</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>외식/회식/간식</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr"/>
+          <t>L_주거/통신</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>L04</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>0102800/SK/SKT5322/가스/수도</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1698,16 +2218,24 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>뜰아래/솔도갈매기/미두야/소바/포베이/10월/조개</t>
+          <t>II_필수생활비</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>외식/회식/간식</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr"/>
+          <t>L_주거/통신</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>L04</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>수신료/전기/케이티/통신/한국전력</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1717,16 +2245,24 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>오케이/웨이업/산자락에/막국수/공간븟/굴사냥</t>
+          <t>III_재량소비</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>외식/회식/간식</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr"/>
+          <t>D_쇼핑</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>D01</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>LIVING/가구/가전/공영쇼핑/그릇</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1736,16 +2272,24 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>닭곰탕/메밀국수/저푸른/닭소리/사계절/두루담채</t>
+          <t>III_재량소비</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>외식/회식/간식</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr"/>
+          <t>D_쇼핑</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>D01</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>나무다움/냉장고/다이소/로웰/마이리얼</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1755,16 +2299,24 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>콩세알/지에스/바로/손만두/멕시카나/청량산/연어</t>
+          <t>III_재량소비</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>외식/회식/간식</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr"/>
+          <t>D_쇼핑</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>D01</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>만물/몰테일/버킷/비와이씨/빈티지</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1774,16 +2326,24 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>빽다방/패류/씨푸드/해장국/김밥/이디야/어시장</t>
+          <t>III_재량소비</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>외식/회식/간식</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr"/>
+          <t>D_쇼핑</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>D01</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>삼성전자/스퀘어/슬립/신세계/어패럴</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -1793,16 +2353,24 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>장수마을/어부장/동춘옥/푸드/공차/이학/두부/모밀</t>
+          <t>III_재량소비</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>외식/회식/간식</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr"/>
+          <t>D_쇼핑</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>D01</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>에이비씨/에이치앤엠/유진/의류/이랜드</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -1812,16 +2380,24 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>반점/닭강정/생오리/떡방아/마장동/자판기/민영</t>
+          <t>III_재량소비</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>외식/회식/간식</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr"/>
+          <t>D_쇼핑</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>D01</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>이케아/자라/제습기/현대아울렛/홈엔</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -1831,16 +2407,24 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>조개/불닭발/직화/던킨/얼음/다정이네/올댓/메고</t>
+          <t>III_재량소비</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>외식/회식/간식</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr"/>
+          <t>D_쇼핑</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>D02</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>CU/GS/목욕탕/미니스톱/부경</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -1850,16 +2434,24 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>미스터/스마일/투썸/대신기업/손만두/휴게소/매반</t>
+          <t>III_재량소비</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>외식/회식/간식</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr"/>
+          <t>D_쇼핑</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>D02</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>세븐일레븐/세탁/세탁소/스테이지/씨유</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -1869,16 +2461,24 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>만강홍/페리카나/최부자네/부대/부대찌게/공간븟</t>
+          <t>III_재량소비</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>외식/회식/간식</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr"/>
+          <t>D_쇼핑</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>D02</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>에스씨/이마트24/지에스/코리아세븐/크린토피아</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -1888,16 +2488,24 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>엔제리너스/리너스/물고기/낙지/송도갈매기/이학</t>
+          <t>III_재량소비</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>외식/회식/간식</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr"/>
+          <t>D_쇼핑</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>D02</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>플라워</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -1907,16 +2515,24 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>병원/의원/치과/약국/건강보험/나사렛/레푸스/메디컬</t>
+          <t>III_재량소비</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>의료비</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr"/>
-      <c r="E78" t="inlineStr"/>
+          <t>D_쇼핑</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>D03</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>G마켓/쇼핑/쇼핑몰/예스이십사/옥션</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -1926,16 +2542,24 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>이비인후과/신경외과/정형외과/엄마손/워너독/이선아</t>
+          <t>III_재량소비</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>의료비</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr"/>
-      <c r="E79" t="inlineStr"/>
+          <t>D_쇼핑</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>D03</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>우정사업/티몬/홈쇼핑</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -1945,16 +2569,24 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>견생냥품/동물의료/안과/의료법인</t>
+          <t>III_재량소비</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>의료비</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr"/>
+          <t>D_여가/미용/뷰티</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>D04</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>CGV/가위/레저/미앤미/스포츠</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -1964,16 +2596,24 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>국세/지방세/세외/주민세/행정안전부/경찰서/연수구청</t>
+          <t>III_재량소비</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>제세공과금</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr"/>
-      <c r="E81" t="inlineStr"/>
+          <t>D_여가/미용/뷰티</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>D04</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>오락/올리브영/중국동방/최성숙/취미</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -1983,16 +2623,24 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>소득세/교육청/소액합산/행정복지/자동차세/취득세</t>
+          <t>III_재량소비</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>제세공과금</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr"/>
-      <c r="E82" t="inlineStr"/>
+          <t>D_여가/미용/뷰티</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>D04</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>꾸리아회계/헤어/휴양</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2002,16 +2650,24 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>지자체/곡공기관/인천광역시/부가가치세/전몰</t>
+          <t>III_재량소비</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>제세공과금</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr"/>
+          <t>D_온/오프라인결재</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>D05</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>KCP/NHN/NICE/결재대행/다날</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2021,16 +2677,24 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>수도/전기/한국전력/가스/통신/관리비/케이티/SK/수신료</t>
+          <t>III_재량소비</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>주거비/통신비</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr"/>
+          <t>D_온/오프라인결재</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>D05</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>모빌리언스/세틀뱅크/스룩/이니시스/케이지</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2040,16 +2704,24 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>주식/부식/반찬/농산물/SSG/건어물/씨푸드/웅이</t>
+          <t>III_재량소비</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>주식비/부식비</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr"/>
+          <t>D_온/오프라인결재</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>D05</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>토스/페이레터/헥토</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2059,16 +2731,24 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>과일/야채/코스트코</t>
+          <t>III_재량소비</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>주식비/부식비</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr"/>
+          <t>D_온/오프라인결재</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>D06</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>ARS/KICC/KIOSK/KIS/SMS</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2078,16 +2758,24 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>정육점/세계로/생선/푸줏간/우아한/성필립보/홈플러스</t>
+          <t>III_재량소비</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>주식비/부식비</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr"/>
-      <c r="E87" t="inlineStr"/>
+          <t>D_온/오프라인결재</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>D06</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>금융결제원/나이스/스마트로/이지체크/코밴</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2097,16 +2785,24 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>초록마을/나눔과어울림/에이치앤케이</t>
+          <t>III_재량소비</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>관계법인</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr"/>
-      <c r="E88" t="inlineStr"/>
+          <t>D_온/오프라인결재</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>D06</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>키오스크/포스결제</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2116,16 +2812,24 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>정경희/한경숙/김은비/김은샘</t>
+          <t>III_재량소비</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>가족관계</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr"/>
-      <c r="E89" t="inlineStr"/>
+          <t>D_온/오프라인결재</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>D07</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>KOPAY/가맹점대금/선지급/수수료차감/정산입금</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2135,16 +2839,24 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>가영현/김경래/김미숙/안재윤/성상현/이미연/조상봉</t>
+          <t>III_재량소비</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>지인관계</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr"/>
+          <t>D_온/오프라인결재</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>D07</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>즉시입금/카드사입금/코페이</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -2154,16 +2866,24 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>최현희/푸른날개/조형호/오석경/전세보증금</t>
+          <t>III_재량소비</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>주거비/통신비</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr"/>
-      <c r="E91" t="inlineStr"/>
+          <t>D_온/오프라인결재</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>D08</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>구글/네이버/삼성페이/스마일페이/애플페이</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -2173,16 +2893,24 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>친애저축/주택금융/NH저축은행</t>
+          <t>III_재량소비</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>대출/상환</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr"/>
-      <c r="E92" t="inlineStr"/>
+          <t>D_온/오프라인결재</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>D08</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>카카오/컬리페이/쿠팡/쿠페이/테무</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -2192,16 +2920,24 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>허영배/김갑용/오흥태/유세움/박제일/민경덕</t>
+          <t>III_재량소비</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>지인관계</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr"/>
-      <c r="E93" t="inlineStr"/>
+          <t>D_온/오프라인결재</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>D08</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>후이즈</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -2211,16 +2947,24 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>김보영/최성숙</t>
+          <t>IV_금융거래</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>지인관계</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr"/>
-      <c r="E94" t="inlineStr"/>
+          <t>F_금융</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>F01</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>311165/433910/433980/NH저축은행/re:이자 \d{2}\.\d{2}~\d{2}\.\d{2}</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2230,16 +2974,24 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>모빌리티/현대해상/메리츠/홍세일/홍천일</t>
+          <t>IV_금융거래</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>차량유지/교통비</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr"/>
-      <c r="E95" t="inlineStr"/>
+          <t>F_금융</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>F01</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>결산이자/대출이자/주택금융/친애저축/카드론</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -2249,16 +3001,24 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>인천광/검찰청/세무서/법무법인/근저당/송달료</t>
+          <t>IV_금융거래</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>제세공과금</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr"/>
-      <c r="E96" t="inlineStr"/>
+          <t>F_금융</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>F01</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>질권/하나캐피탈</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -2268,16 +3028,24 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>박우석/소담산업/문영/차성호/정병용</t>
+          <t>IV_금융거래</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>지인관계</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr"/>
-      <c r="E97" t="inlineStr"/>
+          <t>F_금융</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>F02</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>ATM/현금</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -2287,16 +3055,24 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>60도2787/경찰청/캐롯/이영숙/하나캐피탈/보험료</t>
+          <t>IV_금융거래</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>차량유지/교통비</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr"/>
-      <c r="E98" t="inlineStr"/>
+          <t>F_금융</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>F03</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>검찰청/경찰서/경찰청/공공기관/교육청</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -2306,16 +3082,24 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>풍림연수/풍림3차/SKT5322/0102800</t>
+          <t>IV_금융거래</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>주거비/통신비</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr"/>
-      <c r="E99" t="inlineStr"/>
+          <t>F_금융</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>F03</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>국세/근저당/법무법인/법원/부가가치세</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -2325,16 +3109,24 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>복지용구/사랑의마을/내과</t>
+          <t>IV_금융거래</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>의료비</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr"/>
-      <c r="E100" t="inlineStr"/>
+          <t>F_금융</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>F03</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>세무서/세외/소득세/소액합산/송달료</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -2344,16 +3136,24 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>신미숙/성상헌/이영복/김난수/송창훈/조미영</t>
+          <t>IV_금융거래</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>지인관계</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr"/>
-      <c r="E101" t="inlineStr"/>
+          <t>F_금융</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>F03</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>연수구청/인천광/인천광역시/자동차세/전몰</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -2363,16 +3163,24 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>433910/433980/311165/대출이자/카드론</t>
+          <t>IV_금융거래</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>대출/상환</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr"/>
-      <c r="E102" t="inlineStr"/>
+          <t>F_금융</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>F03</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>주민세/지방세/지자체/취득세/행정복지</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -2382,16 +3190,24 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>주유비/29가8142/60도2787/도로</t>
+          <t>IV_금융거래</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>차량유지/교통비</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr"/>
-      <c r="E103" t="inlineStr"/>
+          <t>F_금융</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>F03</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>행정안전부</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -2401,16 +3217,24 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>김민설/박형수/고남준/강계영</t>
+          <t>V_인적거래</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>지인관계</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr"/>
-      <c r="E104" t="inlineStr"/>
+          <t>P_인적</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>김도이/김승민/김은비/김은샘/김은솔</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -2420,16 +3244,24 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>이니시스/메머드/에이치앤엠/G마켓</t>
+          <t>V_인적거래</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>기타잡비</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr"/>
-      <c r="E105" t="inlineStr"/>
+          <t>P_인적</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>김이제/정경희/한경숙</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -2439,16 +3271,24 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>이비인후과/신경외과/정형외과/엄마손/워너독</t>
+          <t>V_인적거래</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>의료비</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr"/>
-      <c r="E106" t="inlineStr"/>
+          <t>P_인적</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>가영현/강계영/고남준/김갑용/김경래</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -2458,16 +3298,24 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>견생냥품/동물의료/안과</t>
+          <t>V_인적거래</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>의료비</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr"/>
-      <c r="E107" t="inlineStr"/>
+          <t>P_인적</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>김난수/김미숙/김민설/김보영/민경덕</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -2477,16 +3325,24 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>신한카드/현대카드/하나카드/국민카드/이음카드/체크카드</t>
+          <t>V_인적거래</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>신용카드</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr"/>
-      <c r="E108" t="inlineStr"/>
+          <t>P_인적</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>박우석/박제일/박형수/서진태/성상헌</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -2496,16 +3352,24 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>ATM/현금</t>
+          <t>V_인적거래</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>현금거래</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr"/>
-      <c r="E109" t="inlineStr"/>
+          <t>P_인적</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>성상현/송창훈/신미숙/안재윤</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -2515,16 +3379,24 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>모바일/펌뱅킹/인터넷/오픈뱅킹/지로/전자금융/신한카드SMS</t>
+          <t>V_인적거래</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>기타거래</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr"/>
-      <c r="E110" t="inlineStr"/>
+          <t>P_인적</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>오영은/오흥태/유세움/유창훈/이미연</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -2534,16 +3406,24 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>김승민/김은솔/김도이/김이제</t>
+          <t>V_인적거래</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>가족관계</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr"/>
-      <c r="E111" t="inlineStr"/>
+          <t>P_인적</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>이영복/정병용/조미영/조상봉</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -2553,16 +3433,24 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>라다/문영/의왕</t>
+          <t>V_인적거래</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>관계법인</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr"/>
-      <c r="E112" t="inlineStr"/>
+          <t>P_인적</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>김종원/박형식/장인숙/차성호/최인수/허영배/허혜영</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -2572,16 +3460,24 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>씨워크/성우서비스</t>
+          <t>V_인적거래</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>주거비/통신비</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr"/>
-      <c r="E113" t="inlineStr"/>
+          <t>P_인적</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>P03</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>나눔과어울림/라다/문영/에이치앤케이/의왕</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -2591,1201 +3487,1047 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>증권/선물/가상자산/빗썸</t>
+          <t>V_인적거래</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>자산투자</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr"/>
-      <c r="E114" t="inlineStr"/>
+          <t>P_인적</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>P03</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>소담산업/초록마을</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>위험도분류</t>
+          <t>계정과목</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>분류1호#분류제외지표_금액 무관_2~10호에 해당하지 않는 거래</t>
+          <t>V_인적거래</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>분류제외지표</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>0.1</v>
+          <t>P_인적</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>김찬식</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>위험도분류</t>
+          <t>계정과목</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>분류1호/</t>
+          <t>VI_고위험항목</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>분류제외지표</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>0.1</v>
+          <t>H_사행/유흥</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>H02</t>
+        </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>023복권/거래소/귀금속/금은방/면세점</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>위험도분류</t>
+          <t>계정과목</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>분류2호#심야폐업지표_(폐업)금액 무관 / (심야)출금액 10만원 이상_폐업, 거래시간이 심야구분</t>
+          <t>VI_고위험항목</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>심야폐업지표</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>0.5</v>
+          <t>H_사행/유흥</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>H02</t>
+        </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>명품/백화점</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>위험도분류</t>
+          <t>계정과목</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>분류2호/</t>
+          <t>VI_고위험항목</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>심야폐업지표</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>0.5</v>
+          <t>H_투자/자산</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>H03</t>
+        </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>가상자산/빗썸</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>위험도분류</t>
+          <t>계정과목</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>분류3호#자료소명지표_출금 500만원 이상_해당 행의 키워드(또는 기타거래)</t>
+          <t>VI_고위험항목</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>자료소명지표</t>
-        </is>
-      </c>
-      <c r="D119" t="n">
-        <v>1</v>
+          <t>H_투자/자산</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>H04</t>
+        </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>5000000</t>
+          <t>선물/증권</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>위험도분류</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>분류3호/키워드 또는 기타거래</t>
-        </is>
-      </c>
+          <t>전처리</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr"/>
       <c r="C120" t="inlineStr">
         <is>
-          <t>자료소명지표</t>
-        </is>
-      </c>
-      <c r="D120" t="n">
-        <v>1</v>
-      </c>
+          <t>023복권</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr">
         <is>
-          <t>5000000</t>
+          <t>023 shop</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>위험도분류</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>분류4호#비정형지표_출금만 300만원 이상, 같은 키워드 3회 이상_해당 특정인(키워드)</t>
-        </is>
-      </c>
+          <t>전처리</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr"/>
       <c r="C121" t="inlineStr">
         <is>
-          <t>비정형지표</t>
-        </is>
-      </c>
-      <c r="D121" t="n">
-        <v>1.5</v>
-      </c>
+          <t>농협</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr">
         <is>
-          <t>3000000</t>
+          <t>HN</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>위험도분류</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>분류4호/</t>
-        </is>
-      </c>
+          <t>전처리</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr"/>
       <c r="C122" t="inlineStr">
         <is>
-          <t>비정형지표</t>
-        </is>
-      </c>
-      <c r="D122" t="n">
-        <v>1.5</v>
-      </c>
+          <t>국민</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr">
         <is>
-          <t>3000000</t>
+          <t>KB</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>위험도분류</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>분류5호#투기성지표_출금만 100만원 이상_증권, 선물, 자산운용, 위탁, 증권입금 등</t>
-        </is>
-      </c>
+          <t>전처리</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr"/>
       <c r="C123" t="inlineStr">
         <is>
-          <t>투기성지표</t>
-        </is>
-      </c>
-      <c r="D123" t="n">
-        <v>2</v>
-      </c>
+          <t>빗썸</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>나눔과어울림</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>위험도분류</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>분류5호/증권/선물/자산운용/위탁/증권입금</t>
-        </is>
-      </c>
+          <t>전처리</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr"/>
       <c r="C124" t="inlineStr">
         <is>
-          <t>투기성지표</t>
-        </is>
-      </c>
-      <c r="D124" t="n">
-        <v>2</v>
-      </c>
+          <t>남동기업명품센터</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>남동기업센터</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>위험도분류</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>분류6호#사기파산지표_출금만 100만원 이상_대부, P2P, 카드깡, 원리금 등</t>
-        </is>
-      </c>
+          <t>전처리</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr"/>
       <c r="C125" t="inlineStr">
         <is>
-          <t>사기파산지표</t>
-        </is>
-      </c>
-      <c r="D125" t="n">
-        <v>2.5</v>
-      </c>
+          <t>김도이</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>도이</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>위험도분류</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>분류6호/대부/P2P/카드깡/원리금</t>
-        </is>
-      </c>
+          <t>전처리</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr"/>
       <c r="C126" t="inlineStr">
         <is>
-          <t>사기파산지표</t>
-        </is>
-      </c>
-      <c r="D126" t="n">
-        <v>2.5</v>
-      </c>
+          <t>성우머니대부</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>성우서비스</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>위험도분류</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>분류7호#가상자산지표_출금만 100만원 이상 (입금 0)_가상자산, 업비트, 빗썸, 코인원 등</t>
-        </is>
-      </c>
+          <t>전처리</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr"/>
       <c r="C127" t="inlineStr">
         <is>
-          <t>가상자산지표</t>
-        </is>
-      </c>
-      <c r="D127" t="n">
-        <v>3</v>
-      </c>
+          <t>씨워크안마</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>씨워크</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>위험도분류</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>분류7호/가상자산/업비트/빗썸/코인원/코빗/VASP/거래소/코인/비트코인/암호화폐</t>
-        </is>
-      </c>
+          <t>전처리</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr"/>
       <c r="C128" t="inlineStr">
         <is>
-          <t>가상자산지표</t>
-        </is>
-      </c>
-      <c r="D128" t="n">
-        <v>3</v>
-      </c>
+          <t>한경숙</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>어머니/시엄마/어머니</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>위험도분류</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>분류8호#자산은닉지표_출금만 100만원 이상 (입금 0)_해외송금, Wise, SWIFT 등</t>
-        </is>
-      </c>
+          <t>전처리</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr"/>
       <c r="C129" t="inlineStr">
         <is>
-          <t>자산은닉지표</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
-        <v>3.5</v>
-      </c>
+          <t>가상자산</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>에이치앤케이산업개발</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>위험도분류</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>분류8호/해외송금/고액현금인출/외화송금/영문성명/Wise/TransferWise/SWIFT</t>
-        </is>
-      </c>
+          <t>전처리</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr"/>
       <c r="C130" t="inlineStr">
         <is>
-          <t>자산은닉지표</t>
-        </is>
-      </c>
-      <c r="D130" t="n">
-        <v>3.5</v>
-      </c>
+          <t>문영안마</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>운영</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>위험도분류</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>분류9호#과소비지표_출금만 50만원 이상 (입금 0)_백화점, 명품, 유흥, 고가가전 등</t>
-        </is>
-      </c>
+          <t>전처리</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr"/>
       <c r="C131" t="inlineStr">
         <is>
-          <t>과소비지표</t>
-        </is>
-      </c>
-      <c r="D131" t="n">
-        <v>4</v>
-      </c>
+          <t>김은샘</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>은샘</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>위험도분류</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>분류9호/백화점/명품/귀금속/유흥/고가가전/고가가구/유흥주점/무도장/콜라텍/댄스홀</t>
-        </is>
-      </c>
+          <t>전처리</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr"/>
       <c r="C132" t="inlineStr">
         <is>
-          <t>과소비지표</t>
-        </is>
-      </c>
-      <c r="D132" t="n">
-        <v>4</v>
-      </c>
+          <t>나사렛마사지</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>의료법인 나사렛의료재단</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>위험도분류</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>분류10호#사행성지표_출금만 30만원 이상 (입금 0)_경마, 복권, 도박, 휴게텔, 안마 등</t>
-        </is>
-      </c>
+          <t>전처리</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr"/>
       <c r="C133" t="inlineStr">
         <is>
-          <t>사행성지표</t>
-        </is>
-      </c>
-      <c r="D133" t="n">
-        <v>5</v>
-      </c>
+          <t>반각</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>전각</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>위험도분류</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>분류10호/휴게텔/키스방/대화방/안마/마사지/사행성/도박/경마/복권/사설도박/도박기계/사행성게임기/오락기구</t>
-        </is>
-      </c>
+          <t>전처리</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr"/>
       <c r="C134" t="inlineStr">
         <is>
-          <t>사행성지표</t>
-        </is>
-      </c>
-      <c r="D134" t="n">
-        <v>5</v>
-      </c>
+          <t>주택금융공사</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>주금공</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>업종분류</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>귀금속 및 관련제품 제조업</t>
-        </is>
-      </c>
+          <t>전처리</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr"/>
       <c r="C135" t="inlineStr">
         <is>
-          <t>자산은닉지표</t>
-        </is>
-      </c>
-      <c r="D135" t="n">
-        <v>3.5</v>
-      </c>
+          <t>(주)</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr">
         <is>
-          <t>369101</t>
+          <t>주식회사/ 주식회사 / 주식회사</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>업종분류</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>기타 오락용품 제조업(유희용구)</t>
-        </is>
-      </c>
+          <t>전처리</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr"/>
       <c r="C136" t="inlineStr">
         <is>
-          <t>사행성지표</t>
-        </is>
-      </c>
-      <c r="D136" t="n">
-        <v>5</v>
-      </c>
+          <t>친애저축P2P</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr">
         <is>
-          <t>369409</t>
+          <t>친애저축</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>업종분류</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>복권 발행 및 판매업(도매)</t>
-        </is>
-      </c>
+          <t>전처리</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr"/>
       <c r="C137" t="inlineStr">
         <is>
-          <t>사행성지표</t>
-        </is>
-      </c>
-      <c r="D137" t="n">
-        <v>5</v>
-      </c>
+          <t>하나유흥주점</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr">
         <is>
-          <t>512293</t>
+          <t>하나오픈에이치</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>업종분류</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>시계 및 귀금속 제품 소매업/523921</t>
-        </is>
-      </c>
+          <t>전처리</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr">
         <is>
-          <t>과소비지표</t>
-        </is>
-      </c>
-      <c r="D138" t="n">
-        <v>4</v>
-      </c>
+          <t>국민은행</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr">
         <is>
-          <t>513921</t>
+          <t>한국주택은행</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>업종분류</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>시계 및 귀금속 제품 소매업/523922</t>
-        </is>
-      </c>
+          <t>전처리</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr"/>
       <c r="C139" t="inlineStr">
         <is>
-          <t>과소비지표</t>
-        </is>
-      </c>
-      <c r="D139" t="n">
-        <v>4</v>
-      </c>
+          <t>현대백화점</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr">
         <is>
-          <t>513922</t>
+          <t>현대해상</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>업종분류</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>시계 및 귀금속 제품 소매업/523923</t>
-        </is>
-      </c>
+          <t>전처리</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr"/>
       <c r="C140" t="inlineStr">
         <is>
-          <t>과소비지표</t>
-        </is>
-      </c>
-      <c r="D140" t="n">
-        <v>4</v>
-      </c>
+          <t>김종원</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr">
         <is>
-          <t>513923</t>
+          <t>전북은행</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>업종분류</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>운동 및 경기용품 소매업(골프장비)</t>
-        </is>
-      </c>
+          <t>전처리</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr"/>
       <c r="C141" t="inlineStr">
         <is>
-          <t>과소비지표</t>
-        </is>
-      </c>
-      <c r="D141" t="n">
-        <v>4</v>
-      </c>
+          <t>한경숙</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr"/>
       <c r="E141" t="inlineStr">
         <is>
-          <t>513931</t>
+          <t>보훈예우수당</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>업종분류</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>시계 및 귀금속 제품 도매업</t>
-        </is>
-      </c>
+          <t>전처리</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr"/>
       <c r="C142" t="inlineStr">
         <is>
-          <t>과소비지표</t>
-        </is>
-      </c>
-      <c r="D142" t="n">
-        <v>4</v>
-      </c>
+          <t>김찬식</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr">
         <is>
-          <t>513934</t>
+          <t>진프랜드</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>업종분류</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>백화점</t>
-        </is>
-      </c>
+          <t>전처리</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr"/>
       <c r="C143" t="inlineStr">
         <is>
-          <t>과소비지표</t>
-        </is>
-      </c>
-      <c r="D143" t="n">
-        <v>4</v>
-      </c>
+          <t>김찬식</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr">
         <is>
-          <t>521910</t>
+          <t>기제산업건설</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>업종분류</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>면세점</t>
-        </is>
-      </c>
+          <t>전처리</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr"/>
       <c r="C144" t="inlineStr">
         <is>
-          <t>과소비지표</t>
-        </is>
-      </c>
-      <c r="D144" t="n">
-        <v>4</v>
-      </c>
+          <t>김찬식</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr">
         <is>
-          <t>521913</t>
+          <t>평가원수당</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>업종분류</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>복권 발행 및 판매업(소매)</t>
-        </is>
-      </c>
+          <t>전처리</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr"/>
       <c r="C145" t="inlineStr">
         <is>
-          <t>사행성지표</t>
-        </is>
-      </c>
-      <c r="D145" t="n">
-        <v>5</v>
-      </c>
+          <t>에이치앤케이</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr">
         <is>
-          <t>522082</t>
+          <t>신한오픈에이치</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>업종분류</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>시계 및 귀금속 소매업(귀금속)</t>
-        </is>
-      </c>
+          <t>후처리</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr"/>
       <c r="C146" t="inlineStr">
         <is>
-          <t>과소비지표</t>
-        </is>
-      </c>
-      <c r="D146" t="n">
-        <v>4</v>
-      </c>
+          <t>(</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr">
         <is>
-          <t>523922</t>
+          <t>((</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>업종분류</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>시계 및 귀금속 소매업(시계)</t>
-        </is>
-      </c>
+          <t>후처리</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr"/>
       <c r="C147" t="inlineStr">
         <is>
-          <t>과소비지표</t>
-        </is>
-      </c>
-      <c r="D147" t="n">
-        <v>4</v>
-      </c>
+          <t>)</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr">
         <is>
-          <t>523923</t>
+          <t>))</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>업종분류</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>게임용구, 인형 및 장난감 소매업</t>
-        </is>
-      </c>
+          <t>후처리</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr"/>
       <c r="C148" t="inlineStr">
         <is>
-          <t>사행성지표</t>
-        </is>
-      </c>
-      <c r="D148" t="n">
-        <v>5</v>
-      </c>
+          <t>space</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr">
         <is>
-          <t>523940</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>업종분류</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>운동 및 경기용품 도매업(골프장비)</t>
-        </is>
-      </c>
+          <t>후처리</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr"/>
       <c r="C149" t="inlineStr">
         <is>
-          <t>과소비지표</t>
-        </is>
-      </c>
-      <c r="D149" t="n">
-        <v>4</v>
-      </c>
+          <t>김은샘</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr">
         <is>
-          <t>523942</t>
+          <t>김김은샘</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>업종분류</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>호텔업</t>
-        </is>
-      </c>
+          <t>신청인</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr"/>
       <c r="C150" t="inlineStr">
         <is>
-          <t>자료소명지표</t>
-        </is>
-      </c>
-      <c r="D150" t="n">
-        <v>1</v>
-      </c>
+          <t>김찬식</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr"/>
       <c r="E150" t="inlineStr">
         <is>
-          <t>551001</t>
+          <t>k30035600@gmail.com/010-3003-5600</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>업종분류</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>일반 유흥 주점업(고급주점)</t>
-        </is>
-      </c>
+          <t>심야구분</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr"/>
       <c r="C151" t="inlineStr">
         <is>
-          <t>과소비지표</t>
-        </is>
-      </c>
-      <c r="D151" t="n">
-        <v>4</v>
-      </c>
+          <t>심야구분</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr">
         <is>
-          <t>552201</t>
+          <t>22:00:00/06:00:00</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>업종분류</t>
+          <t>위험도분류</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>일반 유흥 주점업(빠, 비어홀, 극장식식당)</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>과소비지표</t>
-        </is>
-      </c>
-      <c r="D152" t="n">
-        <v>4</v>
+          <t>사행성지표</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>300000</t>
+        </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>552202</t>
+          <t>분류10호#사행성지표_출금만 30만원 이상 (입금 0)_경마, 복권, 도박, 휴게텔, 안마 등</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>업종분류</t>
+          <t>위험도분류</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>무도 유흥 주점업</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>과소비지표</t>
-        </is>
-      </c>
-      <c r="D153" t="n">
-        <v>4</v>
+          <t>사행성지표</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>300000</t>
+        </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>552203</t>
+          <t>분류10호/휴게텔/키스방/대화방/안마/마사지/사행성/도박/경마/복권/사설도박/도박기계/사행성게임기/오락기구</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>업종분류</t>
+          <t>위험도분류</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>일반 유흥 주점업(관광음식잠)</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>과소비지표</t>
-        </is>
-      </c>
-      <c r="D154" t="n">
-        <v>4</v>
+          <t>분류제외지표</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>552204</t>
+          <t>분류1호#분류제외지표_금액 무관_2~10호에 해당하지 않는 거래</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>업종분류</t>
+          <t>위험도분류</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>일반 유흥 주점업(기타 유흥)</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>과소비지표</t>
-        </is>
-      </c>
-      <c r="D155" t="n">
-        <v>4</v>
+          <t>분류제외지표</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>552206</t>
+          <t>분류1호/</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>업종분류</t>
+          <t>위험도분류</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>기타 주점업(단란주점)</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>과소비지표</t>
-        </is>
-      </c>
-      <c r="D156" t="n">
-        <v>4</v>
+          <t>심야폐업지표</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>100000</t>
+        </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>552207</t>
+          <t>분류2호#심야폐업지표_(폐업)금액 무관 / (심야)출금액 10만원 이상_폐업, 거래시간이 심야구분</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>업종분류</t>
+          <t>위험도분류</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>기타 주점업(서양식 주점)</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>과소비지표</t>
-        </is>
-      </c>
-      <c r="D157" t="n">
-        <v>4</v>
+          <t>심야폐업지표</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>100000</t>
+        </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>552208</t>
+          <t>분류2호/</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>업종분류</t>
+          <t>위험도분류</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>기타 주점업</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>과소비지표</t>
-        </is>
-      </c>
-      <c r="D158" t="n">
-        <v>4</v>
+          <t>자료소명지표</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>5000000</t>
+        </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>552209</t>
+          <t>분류3호#자료소명지표_출금 500만원 이상_해당 행의 키워드(또는 기타거래)</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>업종분류</t>
+          <t>위험도분류</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>기타 주점업(소주방)</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>과소비지표</t>
-        </is>
-      </c>
-      <c r="D159" t="n">
-        <v>4</v>
+          <t>자료소명지표</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>5000000</t>
+        </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>552210</t>
+          <t>분류3호/키워드 또는 기타거래</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>업종분류</t>
+          <t>위험도분류</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>기타 주점업(홀덤펍)</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>과소비지표</t>
-        </is>
-      </c>
-      <c r="D160" t="n">
-        <v>4</v>
+          <t>비정형지표</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>3000000</t>
+        </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>552211</t>
+          <t>분류4호#비정형지표_출금만 300만원 이상, 같은 키워드 3회 이상_해당 특정인(키워드)</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>업종분류</t>
+          <t>위험도분류</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>항공 여객 운송업</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>자료소명지표</t>
-        </is>
-      </c>
-      <c r="D161" t="n">
-        <v>1</v>
+          <t>비정형지표</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>3000000</t>
+        </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>621000</t>
+          <t>분류4호/</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>업종분류</t>
+          <t>위험도분류</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>그 외 기타 금융 지원 서비스업/671201</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -3793,24 +4535,26 @@
           <t>투기성지표</t>
         </is>
       </c>
-      <c r="D162" t="n">
-        <v>2</v>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>1000000</t>
+        </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>671201</t>
+          <t>분류5호#투기성지표_출금만 100만원 이상_증권, 선물, 자산운용, 위탁, 증권입금 등</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>업종분류</t>
+          <t>위험도분류</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>증권 중개업</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -3818,199 +4562,215 @@
           <t>투기성지표</t>
         </is>
       </c>
-      <c r="D163" t="n">
-        <v>2</v>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>1000000</t>
+        </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>671202</t>
+          <t>분류5호/증권/선물/자산운용/위탁/증권입금</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>업종분류</t>
+          <t>위험도분류</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>선물 중개업</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>투기성지표</t>
-        </is>
-      </c>
-      <c r="D164" t="n">
-        <v>2</v>
+          <t>사기파산지표</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>1000000</t>
+        </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>671203</t>
+          <t>분류6호#사기파산지표_출금만 100만원 이상_대부, P2P, 카드깡, 원리금 등</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>업종분류</t>
+          <t>위험도분류</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>그 외 기타 금융 지원 서비스업/671900</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>투기성지표</t>
-        </is>
-      </c>
-      <c r="D165" t="n">
-        <v>2</v>
+          <t>사기파산지표</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>1000000</t>
+        </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>671900</t>
+          <t>분류6호/대부/P2P/카드깡/원리금</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>업종분류</t>
+          <t>위험도분류</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>금융시장 관리업</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>투기성지표</t>
-        </is>
-      </c>
-      <c r="D166" t="n">
-        <v>2</v>
+          <t>가상자산지표</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>1000000</t>
+        </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>671901</t>
+          <t>분류7호#가상자산지표_출금만 100만원 이상 (입금 0)_가상자산, 업비트, 빗썸, 코인원 등</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>업종분류</t>
+          <t>위험도분류</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>증권 발행, 관리, 보관 및 거래 지원 서비스업</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>투기성지표</t>
-        </is>
-      </c>
-      <c r="D167" t="n">
-        <v>2</v>
+          <t>가상자산지표</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>1000000</t>
+        </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>671902</t>
+          <t>분류7호/가상자산/업비트/빗썸/코인원/코빗/VASP/거래소/코인/비트코인/암호화폐</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>업종분류</t>
+          <t>위험도분류</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>투자 자문업 및 투자 일임업</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>투기성지표</t>
-        </is>
-      </c>
-      <c r="D168" t="n">
-        <v>2</v>
+          <t>자산은닉지표</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>1000000</t>
+        </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>671903</t>
+          <t>분류8호#자산은닉지표_출금만 100만원 이상 (입금 0)_해외송금, Wise, SWIFT 등</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>업종분류</t>
+          <t>위험도분류</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>그 외 기타 정보 서비스업</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>가상자산지표</t>
-        </is>
-      </c>
-      <c r="D169" t="n">
-        <v>3</v>
+          <t>자산은닉지표</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>1000000</t>
+        </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>724002</t>
+          <t>분류8호/해외송금/고액현금인출/외화송금/영문성명/Wise/TransferWise/SWIFT</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>업종분류</t>
+          <t>위험도분류</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>무도장 운영업</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>사행성지표</t>
-        </is>
-      </c>
-      <c r="D170" t="n">
-        <v>5</v>
+          <t>과소비지표</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>500000</t>
+        </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>921904</t>
+          <t>분류9호#과소비지표_출금만 50만원 이상 (입금 0)_백화점, 명품, 유흥, 고가가전 등</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>업종분류</t>
+          <t>위험도분류</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>골프장 운영업</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -4018,12 +4778,14 @@
           <t>과소비지표</t>
         </is>
       </c>
-      <c r="D171" t="n">
-        <v>4</v>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>500000</t>
+        </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>924307</t>
+          <t>분류9호/백화점/명품/귀금속/유흥/고가가전/고가가구/유흥주점/무도장/콜라텍/댄스홀</t>
         </is>
       </c>
     </row>
@@ -4035,20 +4797,22 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>골프 연습장 운영업(야외)</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>과소비지표</t>
-        </is>
-      </c>
-      <c r="D172" t="n">
-        <v>4</v>
+          <t>사행성지표</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>523940</t>
+        </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>924307</t>
+          <t>게임용구, 인형 및 장난감 소매업</t>
         </is>
       </c>
     </row>
@@ -4060,20 +4824,22 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>과소비지표</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>924308</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
           <t>골프 연습장 운영업(실내)</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>과소비지표</t>
-        </is>
-      </c>
-      <c r="D173" t="n">
-        <v>4</v>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>924308</t>
         </is>
       </c>
     </row>
@@ -4085,20 +4851,22 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>기타 오락장 운영업(전화방)</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>사행성지표</t>
-        </is>
-      </c>
-      <c r="D174" t="n">
-        <v>5</v>
+          <t>과소비지표</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>924307</t>
+        </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>924904</t>
+          <t>골프 연습장 운영업(야외)</t>
         </is>
       </c>
     </row>
@@ -4110,20 +4878,22 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>복권 발행 및 판매업(발행)</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>사행성지표</t>
-        </is>
-      </c>
-      <c r="D175" t="n">
-        <v>5</v>
+          <t>과소비지표</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>924307</t>
+        </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>924906</t>
+          <t>골프장 운영업</t>
         </is>
       </c>
     </row>
@@ -4135,20 +4905,22 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>기타 오락장 운영업(보드게임방)</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>사행성지표</t>
-        </is>
-      </c>
-      <c r="D176" t="n">
-        <v>5</v>
+          <t>자산은닉지표</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>369101</t>
+        </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>924913</t>
+          <t>귀금속 및 관련제품 제조업</t>
         </is>
       </c>
     </row>
@@ -4160,20 +4932,1021 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>투기성지표</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>671201</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>그 외 기타 금융 지원 서비스업</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>업종분류</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>투기성지표</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>671900</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>그 외 기타 금융 지원 서비스업</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>업종분류</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>가상자산지표</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>724002</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>그 외 기타 정보 서비스업</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>업종분류</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>투기성지표</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>671901</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>금융시장 관리업</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>업종분류</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>사행성지표</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>924917</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
           <t>기타 사행시설 관리 및 운영업</t>
         </is>
       </c>
-      <c r="C177" t="inlineStr">
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>업종분류</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
         <is>
           <t>사행성지표</t>
         </is>
       </c>
-      <c r="D177" t="n">
-        <v>5</v>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>924917</t>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>369409</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>기타 오락용품 제조업(유희용구)</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>업종분류</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>사행성지표</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>924913</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>기타 오락장 운영업(보드게임방)</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>업종분류</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>사행성지표</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>924904</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>기타 오락장 운영업(전화방)</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>업종분류</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>과소비지표</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>552209</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>기타 주점업</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>업종분류</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>과소비지표</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>552207</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>기타 주점업(단란주점)</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>업종분류</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>과소비지표</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>552208</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>기타 주점업(서양식 주점)</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>업종분류</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>과소비지표</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>552210</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>기타 주점업(소주방)</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>업종분류</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>과소비지표</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>552211</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>기타 주점업(홀덤펍)</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>업종분류</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>과소비지표</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>521913</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>면세점</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>업종분류</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>과소비지표</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>552203</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>무도 유흥 주점업</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>업종분류</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>사행성지표</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>921904</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>무도장 운영업</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>업종분류</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>과소비지표</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>521910</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>백화점</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>업종분류</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>사행성지표</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>512293</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>복권 발행 및 판매업(도매)</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>업종분류</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>사행성지표</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>924906</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>복권 발행 및 판매업(발행)</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>업종분류</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>사행성지표</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>522082</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>복권 발행 및 판매업(소매)</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>업종분류</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>투기성지표</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>671203</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>선물 중개업</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>업종분류</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>과소비지표</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>523922</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>시계 및 귀금속 소매업(귀금속)</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>업종분류</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>과소비지표</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>523923</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>시계 및 귀금속 소매업(시계)</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>업종분류</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>과소비지표</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>513934</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>시계 및 귀금속 제품 도매업</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>업종분류</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>과소비지표</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>513921</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>시계 및 귀금속 제품 소매업</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>업종분류</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>과소비지표</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>513922</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>시계 및 귀금속 제품 소매업</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>업종분류</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>과소비지표</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>513923</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>시계 및 귀금속 제품 소매업</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>업종분류</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>과소비지표</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>523942</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>운동 및 경기용품 도매업(골프장비)</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>업종분류</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>과소비지표</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>513931</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>운동 및 경기용품 소매업(골프장비)</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>업종분류</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>과소비지표</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>552201</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>일반 유흥 주점업(고급주점)</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>업종분류</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>과소비지표</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>552204</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>일반 유흥 주점업(관광음식잠)</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>업종분류</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>과소비지표</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>552206</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>일반 유흥 주점업(기타 유흥)</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>업종분류</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>과소비지표</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>552202</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>일반 유흥 주점업(빠, 비어홀, 극장식식당)</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>업종분류</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>투기성지표</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>671902</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>증권 발행, 관리, 보관 및 거래 지원 서비스업</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>업종분류</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>투기성지표</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>671202</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>증권 중개업</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>업종분류</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>투기성지표</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>671903</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>투자 자문업 및 투자 일임업</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>업종분류</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>자료소명지표</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>621000</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>항공 여객 운송업</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>업종분류</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>자료소명지표</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>551001</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>호텔업</t>
         </is>
       </c>
     </row>
